--- a/erp-server/erp-server-file/src/main/resources/excel/wms/reportOrderDemandDetail.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/reportOrderDemandDetail.xlsx
@@ -59,7 +59,7 @@
     <t>更新时间</t>
   </si>
   <si>
-    <t>{.orderTypeName}</t>
+    <t>{.sourceTypeName}</t>
   </si>
   <si>
     <t>{.sourceCode}</t>
